--- a/examples/synthetic_distillation/lab_results.xlsx
+++ b/examples/synthetic_distillation/lab_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:C317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,15 +424,10 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Result_Timestamp</t>
+          <t>Product_Composition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>Product_Composition</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
         <is>
           <t>Sample_ID</t>
         </is>
@@ -444,15 +439,10 @@
           <t>2026-03-02 01:53</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-02 02:44</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="n">
         <v>0.9852</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>L0001</t>
         </is>
@@ -464,15 +454,10 @@
           <t>2026-03-02 04:09</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-02 05:44</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="n">
         <v>0.9841</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>L0002</t>
         </is>
@@ -484,15 +469,10 @@
           <t>2026-03-02 06:02</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-02 07:21</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="n">
         <v>0.9846</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>L0003</t>
         </is>
@@ -504,15 +484,10 @@
           <t>2026-03-02 07:55</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-02 08:59</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>L0004</t>
         </is>
@@ -524,15 +499,10 @@
           <t>2026-03-02 09:57</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-02 11:26</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="n">
         <v>0.9797</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>L0005</t>
         </is>
@@ -544,15 +514,10 @@
           <t>2026-03-02 12:09</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-02 13:38</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" t="n">
         <v>0.9802</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>L0006</t>
         </is>
@@ -564,15 +529,10 @@
           <t>2026-03-02 14:05</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:11</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" t="n">
         <v>0.9796</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>L0007</t>
         </is>
@@ -584,15 +544,10 @@
           <t>2026-03-02 16:02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-02 16:50</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" t="n">
         <v>0.9828</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>L0008</t>
         </is>
@@ -604,15 +559,10 @@
           <t>2026-03-02 17:51</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-02 19:36</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>L0009</t>
         </is>
@@ -624,15 +574,10 @@
           <t>2026-03-02 19:51</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-02 21:34</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" t="n">
         <v>0.9864000000000001</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>L0010</t>
         </is>
@@ -644,15 +589,10 @@
           <t>2026-03-02 22:00</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-02 23:51</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" t="n">
         <v>0.9867</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>L0011</t>
         </is>
@@ -664,15 +604,10 @@
           <t>2026-03-02 23:58</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-03 01:18</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>L0012</t>
         </is>
@@ -684,15 +619,10 @@
           <t>2026-03-03 01:52</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-03 03:52</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>L0013</t>
         </is>
@@ -704,15 +634,10 @@
           <t>2026-03-03 04:05</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-03 04:50</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" t="n">
         <v>0.9799</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>L0014</t>
         </is>
@@ -724,15 +649,10 @@
           <t>2026-03-03 05:59</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-03 06:51</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>L0015</t>
         </is>
@@ -744,15 +664,10 @@
           <t>2026-03-03 07:54</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-03 09:28</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17" t="n">
         <v>0.9871</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>L0016</t>
         </is>
@@ -764,15 +679,10 @@
           <t>2026-03-03 09:57</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-03 11:01</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18" t="n">
         <v>0.9794</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>L0017</t>
         </is>
@@ -784,15 +694,10 @@
           <t>2026-03-03 11:59</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-03 13:40</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>L0018</t>
         </is>
@@ -804,15 +709,10 @@
           <t>2026-03-03 13:50</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-03 14:56</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="B20" t="n">
         <v>0.9807</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>L0019</t>
         </is>
@@ -824,15 +724,10 @@
           <t>2026-03-03 15:54</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-03 16:52</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21" t="n">
         <v>0.9798</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>L0020</t>
         </is>
@@ -844,15 +739,10 @@
           <t>2026-03-03 17:59</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-03 19:58</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22" t="n">
         <v>0.982</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>L0021</t>
         </is>
@@ -864,15 +754,10 @@
           <t>2026-03-03 20:04</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-03 21:01</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23" t="n">
         <v>0.9781</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>L0022</t>
         </is>
@@ -884,15 +769,10 @@
           <t>2026-03-03 22:01</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-03 23:28</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24" t="n">
         <v>0.9843</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>L0023</t>
         </is>
@@ -904,15 +784,10 @@
           <t>2026-03-04 00:08</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-04 01:27</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25" t="n">
         <v>0.986</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>L0024</t>
         </is>
@@ -924,15 +799,10 @@
           <t>2026-03-04 02:04</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-04 03:49</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26" t="n">
         <v>0.9861</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>L0025</t>
         </is>
@@ -944,15 +814,10 @@
           <t>2026-03-04 04:03</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-04 04:55</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="B27" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>L0026</t>
         </is>
@@ -964,15 +829,10 @@
           <t>2026-03-04 06:03</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-04 07:16</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28" t="n">
         <v>0.9823</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>L0027</t>
         </is>
@@ -984,15 +844,10 @@
           <t>2026-03-04 08:09</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-04 09:52</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29" t="n">
         <v>0.9808</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>L0028</t>
         </is>
@@ -1004,15 +859,10 @@
           <t>2026-03-04 10:03</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-04 10:51</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="B30" t="n">
         <v>0.9858</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>L0029</t>
         </is>
@@ -1024,15 +874,10 @@
           <t>2026-03-04 11:57</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-04 13:36</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+      <c r="B31" t="n">
         <v>0.9865</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>L0030</t>
         </is>
@@ -1044,15 +889,10 @@
           <t>2026-03-04 13:50</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-04 15:33</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32" t="n">
         <v>0.9842</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>L0031</t>
         </is>
@@ -1064,15 +904,10 @@
           <t>2026-03-04 15:54</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-04 17:01</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="B33" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>L0032</t>
         </is>
@@ -1084,15 +919,10 @@
           <t>2026-03-04 17:53</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-04 19:33</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+      <c r="B34" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>L0033</t>
         </is>
@@ -1104,15 +934,10 @@
           <t>2026-03-04 19:52</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-04 21:45</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="B35" t="n">
         <v>0.9818</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>L0034</t>
         </is>
@@ -1124,15 +949,10 @@
           <t>2026-03-04 21:56</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-04 23:06</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="B36" t="n">
         <v>0.981</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>L0035</t>
         </is>
@@ -1144,15 +964,10 @@
           <t>2026-03-05 00:10</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-05 01:26</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+      <c r="B37" t="n">
         <v>0.9851</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>L0036</t>
         </is>
@@ -1164,15 +979,10 @@
           <t>2026-03-05 01:55</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-05 03:21</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+      <c r="B38" t="n">
         <v>0.9802999999999999</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>L0037</t>
         </is>
@@ -1184,15 +994,10 @@
           <t>2026-03-05 03:50</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-05 04:46</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+      <c r="B39" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>L0038</t>
         </is>
@@ -1204,15 +1009,10 @@
           <t>2026-03-05 06:04</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-05 06:50</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+      <c r="B40" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>L0039</t>
         </is>
@@ -1224,15 +1024,10 @@
           <t>2026-03-05 07:53</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-05 09:17</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+      <c r="B41" t="n">
         <v>0.9804</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>L0040</t>
         </is>
@@ -1244,15 +1039,10 @@
           <t>2026-03-05 09:53</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-05 11:15</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+      <c r="B42" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>L0041</t>
         </is>
@@ -1264,15 +1054,10 @@
           <t>2026-03-05 11:50</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-05 12:43</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43" t="n">
         <v>0.9772</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>L0042</t>
         </is>
@@ -1284,15 +1069,10 @@
           <t>2026-03-05 13:55</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-05 15:37</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44" t="n">
         <v>0.9751</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>L0043</t>
         </is>
@@ -1304,15 +1084,10 @@
           <t>2026-03-05 16:02</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-05 16:49</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45" t="n">
         <v>0.976</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>L0044</t>
         </is>
@@ -1324,15 +1099,10 @@
           <t>2026-03-05 18:08</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-05 19:40</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46" t="n">
         <v>0.9777</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>L0045</t>
         </is>
@@ -1344,15 +1114,10 @@
           <t>2026-03-05 19:50</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-05 21:49</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+      <c r="B47" t="n">
         <v>0.9789</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>L0046</t>
         </is>
@@ -1364,15 +1129,10 @@
           <t>2026-03-05 21:51</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-05 23:28</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48" t="n">
         <v>0.9736</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>L0047</t>
         </is>
@@ -1384,15 +1144,10 @@
           <t>2026-03-06 00:03</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-06 01:39</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+      <c r="B49" t="n">
         <v>0.9787</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>L0048</t>
         </is>
@@ -1404,15 +1159,10 @@
           <t>2026-03-06 02:02</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-06 03:28</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
+      <c r="B50" t="n">
         <v>0.9802999999999999</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>L0049</t>
         </is>
@@ -1424,15 +1174,10 @@
           <t>2026-03-06 04:08</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-06 05:56</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
+      <c r="B51" t="n">
         <v>0.979</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>L0050</t>
         </is>
@@ -1444,15 +1189,10 @@
           <t>2026-03-06 05:55</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-06 07:46</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+      <c r="B52" t="n">
         <v>0.9802</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>L0051</t>
         </is>
@@ -1464,15 +1204,10 @@
           <t>2026-03-06 08:08</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:01</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
+      <c r="B53" t="n">
         <v>0.9869</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>L0052</t>
         </is>
@@ -1484,15 +1219,10 @@
           <t>2026-03-06 10:08</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-06 11:56</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
+      <c r="B54" t="n">
         <v>0.9841</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>L0053</t>
         </is>
@@ -1504,15 +1234,10 @@
           <t>2026-03-06 11:54</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-06 12:55</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
+      <c r="B55" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>L0054</t>
         </is>
@@ -1524,15 +1249,10 @@
           <t>2026-03-06 14:08</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-06 14:57</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
+      <c r="B56" t="n">
         <v>0.9802</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>L0055</t>
         </is>
@@ -1544,15 +1264,10 @@
           <t>2026-03-06 15:53</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-03-06 16:51</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+      <c r="B57" t="n">
         <v>0.9809</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>L0056</t>
         </is>
@@ -1564,15 +1279,10 @@
           <t>2026-03-06 17:54</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-03-06 19:18</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58" t="n">
         <v>0.9828</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>L0057</t>
         </is>
@@ -1584,15 +1294,10 @@
           <t>2026-03-06 20:01</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:00</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
+      <c r="B59" t="n">
         <v>0.9835</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>L0058</t>
         </is>
@@ -1604,15 +1309,10 @@
           <t>2026-03-06 21:54</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-03-06 23:43</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="B60" t="n">
         <v>0.9865</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>L0059</t>
         </is>
@@ -1624,15 +1324,10 @@
           <t>2026-03-07 00:02</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-03-07 00:50</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
+      <c r="B61" t="n">
         <v>0.9855</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>L0060</t>
         </is>
@@ -1644,15 +1339,10 @@
           <t>2026-03-07 02:03</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-03-07 03:43</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
+      <c r="B62" t="n">
         <v>0.9877</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>L0061</t>
         </is>
@@ -1664,15 +1354,10 @@
           <t>2026-03-07 04:01</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-03-07 05:25</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
+      <c r="B63" t="n">
         <v>0.9826</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>L0062</t>
         </is>
@@ -1684,15 +1369,10 @@
           <t>2026-03-07 05:57</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-03-07 06:51</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
+      <c r="B64" t="n">
         <v>0.9828</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>L0063</t>
         </is>
@@ -1704,15 +1384,10 @@
           <t>2026-03-07 08:06</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-03-07 09:32</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
+      <c r="B65" t="n">
         <v>0.9794</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>L0064</t>
         </is>
@@ -1724,15 +1399,10 @@
           <t>2026-03-07 10:06</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-03-07 11:50</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
+      <c r="B66" t="n">
         <v>0.9814000000000001</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>L0065</t>
         </is>
@@ -1744,15 +1414,10 @@
           <t>2026-03-07 12:05</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-03-07 12:57</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
+      <c r="B67" t="n">
         <v>0.981</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>L0066</t>
         </is>
@@ -1764,15 +1429,10 @@
           <t>2026-03-07 14:07</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-03-07 14:52</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
+      <c r="B68" t="n">
         <v>0.9873</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>L0067</t>
         </is>
@@ -1784,15 +1444,10 @@
           <t>2026-03-07 16:09</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-03-07 17:40</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
+      <c r="B69" t="n">
         <v>0.9873</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>L0068</t>
         </is>
@@ -1804,15 +1459,10 @@
           <t>2026-03-07 17:51</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-03-07 19:51</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
+      <c r="B70" t="n">
         <v>0.9814000000000001</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>L0069</t>
         </is>
@@ -1824,15 +1474,10 @@
           <t>2026-03-07 19:55</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-03-07 21:07</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
+      <c r="B71" t="n">
         <v>0.9797</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>L0070</t>
         </is>
@@ -1844,15 +1489,10 @@
           <t>2026-03-08 19:50</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-03-08 21:24</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
+      <c r="B72" t="n">
         <v>0.9806</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>L0071</t>
         </is>
@@ -1864,15 +1504,10 @@
           <t>2026-03-08 21:50</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-03-08 23:38</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
+      <c r="B73" t="n">
         <v>0.979</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>L0072</t>
         </is>
@@ -1884,15 +1519,10 @@
           <t>2026-03-09 00:02</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-03-09 01:50</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
+      <c r="B74" t="n">
         <v>0.9778</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>L0073</t>
         </is>
@@ -1904,15 +1534,10 @@
           <t>2026-03-09 01:53</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-03-09 03:42</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
+      <c r="B75" t="n">
         <v>0.9804</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>L0074</t>
         </is>
@@ -1924,15 +1549,10 @@
           <t>2026-03-09 04:09</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-03-09 05:32</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
+      <c r="B76" t="n">
         <v>0.9818</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>L0075</t>
         </is>
@@ -1944,15 +1564,10 @@
           <t>2026-03-09 05:50</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-03-09 06:39</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
+      <c r="B77" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>L0076</t>
         </is>
@@ -1964,15 +1579,10 @@
           <t>2026-03-09 07:51</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-03-09 09:41</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
+      <c r="B78" t="n">
         <v>0.9829</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>L0077</t>
         </is>
@@ -1984,15 +1594,10 @@
           <t>2026-03-09 10:08</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-03-09 11:10</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
+      <c r="B79" t="n">
         <v>0.9828</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>L0078</t>
         </is>
@@ -2004,15 +1609,10 @@
           <t>2026-03-09 11:51</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-03-09 12:59</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
+      <c r="B80" t="n">
         <v>0.9839</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>L0079</t>
         </is>
@@ -2024,15 +1624,10 @@
           <t>2026-03-09 14:09</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-03-09 15:30</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
+      <c r="B81" t="n">
         <v>0.9813</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>L0080</t>
         </is>
@@ -2044,15 +1639,10 @@
           <t>2026-03-09 16:10</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-03-09 17:43</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
+      <c r="B82" t="n">
         <v>0.9863</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>L0081</t>
         </is>
@@ -2064,15 +1654,10 @@
           <t>2026-03-09 17:55</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-03-09 19:55</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
+      <c r="B83" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>L0082</t>
         </is>
@@ -2084,15 +1669,10 @@
           <t>2026-03-09 19:57</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-03-09 21:06</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
+      <c r="B84" t="n">
         <v>0.9833</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>L0083</t>
         </is>
@@ -2104,15 +1684,10 @@
           <t>2026-03-09 21:59</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-03-09 23:49</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
+      <c r="B85" t="n">
         <v>0.9844000000000001</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>L0084</t>
         </is>
@@ -2124,15 +1699,10 @@
           <t>2026-03-10 00:10</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-03-10 02:08</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
+      <c r="B86" t="n">
         <v>0.9895</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>L0085</t>
         </is>
@@ -2144,15 +1714,10 @@
           <t>2026-03-10 02:03</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-03-10 03:45</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
+      <c r="B87" t="n">
         <v>0.9799</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>L0086</t>
         </is>
@@ -2164,15 +1729,10 @@
           <t>2026-03-10 04:00</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-03-10 05:26</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
+      <c r="B88" t="n">
         <v>0.9772</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>L0087</t>
         </is>
@@ -2184,15 +1744,10 @@
           <t>2026-03-10 05:56</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-03-10 07:55</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
+      <c r="B89" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>L0088</t>
         </is>
@@ -2204,15 +1759,10 @@
           <t>2026-03-10 07:53</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-03-10 09:53</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
+      <c r="B90" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>L0089</t>
         </is>
@@ -2224,15 +1774,10 @@
           <t>2026-03-10 10:03</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-03-10 11:44</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
+      <c r="B91" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>L0090</t>
         </is>
@@ -2244,15 +1789,10 @@
           <t>2026-03-10 11:52</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-03-10 13:11</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
+      <c r="B92" t="n">
         <v>0.984</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>L0091</t>
         </is>
@@ -2264,15 +1804,10 @@
           <t>2026-03-10 14:08</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-03-10 15:26</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
+      <c r="B93" t="n">
         <v>0.9801</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>L0092</t>
         </is>
@@ -2284,15 +1819,10 @@
           <t>2026-03-10 16:06</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-03-10 17:21</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
+      <c r="B94" t="n">
         <v>0.9829</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>L0093</t>
         </is>
@@ -2304,15 +1834,10 @@
           <t>2026-03-10 18:00</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-03-10 19:52</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
+      <c r="B95" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>L0094</t>
         </is>
@@ -2324,15 +1849,10 @@
           <t>2026-03-10 19:59</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-03-10 20:55</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
+      <c r="B96" t="n">
         <v>0.9817</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>L0095</t>
         </is>
@@ -2344,15 +1864,10 @@
           <t>2026-03-10 21:51</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-03-10 22:56</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
+      <c r="B97" t="n">
         <v>0.9833</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>L0096</t>
         </is>
@@ -2364,15 +1879,10 @@
           <t>2026-03-11 00:05</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-03-11 02:04</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
+      <c r="B98" t="n">
         <v>0.977</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>L0097</t>
         </is>
@@ -2384,15 +1894,10 @@
           <t>2026-03-11 01:55</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-03-11 03:54</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
+      <c r="B99" t="n">
         <v>0.9792999999999999</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>L0098</t>
         </is>
@@ -2404,15 +1909,10 @@
           <t>2026-03-11 04:07</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-03-11 05:42</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
+      <c r="B100" t="n">
         <v>0.9826</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>L0099</t>
         </is>
@@ -2424,15 +1924,10 @@
           <t>2026-03-11 05:59</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-03-11 07:56</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
+      <c r="B101" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>L0100</t>
         </is>
@@ -2444,15 +1939,10 @@
           <t>2026-03-11 07:59</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-03-11 09:45</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
+      <c r="B102" t="n">
         <v>0.984</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>L0101</t>
         </is>
@@ -2464,15 +1954,10 @@
           <t>2026-03-11 09:58</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-03-11 11:17</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
+      <c r="B103" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>L0102</t>
         </is>
@@ -2484,15 +1969,10 @@
           <t>2026-03-11 11:57</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-03-11 13:17</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
+      <c r="B104" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>L0103</t>
         </is>
@@ -2504,15 +1984,10 @@
           <t>2026-03-11 13:56</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-03-11 15:03</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
+      <c r="B105" t="n">
         <v>0.9819</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>L0104</t>
         </is>
@@ -2524,15 +1999,10 @@
           <t>2026-03-11 15:53</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-03-11 16:59</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
+      <c r="B106" t="n">
         <v>0.9841</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>L0105</t>
         </is>
@@ -2544,15 +2014,10 @@
           <t>2026-03-11 18:00</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-03-11 19:27</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
+      <c r="B107" t="n">
         <v>0.9858</v>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>L0106</t>
         </is>
@@ -2564,15 +2029,10 @@
           <t>2026-03-11 19:54</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-03-11 20:51</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
+      <c r="B108" t="n">
         <v>0.9877</v>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>L0107</t>
         </is>
@@ -2584,15 +2044,10 @@
           <t>2026-03-11 21:58</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2026-03-11 23:52</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
+      <c r="B109" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>L0108</t>
         </is>
@@ -2604,15 +2059,10 @@
           <t>2026-03-11 23:58</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026-03-12 01:39</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
+      <c r="B110" t="n">
         <v>0.9782</v>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>L0109</t>
         </is>
@@ -2624,15 +2074,10 @@
           <t>2026-03-12 02:08</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2026-03-12 03:36</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
+      <c r="B111" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>L0110</t>
         </is>
@@ -2644,15 +2089,10 @@
           <t>2026-03-12 04:05</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2026-03-12 04:56</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
+      <c r="B112" t="n">
         <v>0.9833</v>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>L0111</t>
         </is>
@@ -2664,15 +2104,10 @@
           <t>2026-03-12 06:06</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2026-03-12 07:05</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
+      <c r="B113" t="n">
         <v>0.98</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>L0112</t>
         </is>
@@ -2684,15 +2119,10 @@
           <t>2026-03-12 07:51</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026-03-12 09:02</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
+      <c r="B114" t="n">
         <v>0.9828</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>L0113</t>
         </is>
@@ -2704,15 +2134,10 @@
           <t>2026-03-12 10:07</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2026-03-12 11:10</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
+      <c r="B115" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>L0114</t>
         </is>
@@ -2724,15 +2149,10 @@
           <t>2026-03-12 11:52</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026-03-12 13:05</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
+      <c r="B116" t="n">
         <v>0.9859</v>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>L0115</t>
         </is>
@@ -2744,15 +2164,10 @@
           <t>2026-03-12 13:59</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2026-03-12 15:50</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
+      <c r="B117" t="n">
         <v>0.9867</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>L0116</t>
         </is>
@@ -2764,15 +2179,10 @@
           <t>2026-03-12 16:01</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2026-03-12 16:54</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
+      <c r="B118" t="n">
         <v>0.9835</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>L0117</t>
         </is>
@@ -2784,15 +2194,10 @@
           <t>2026-03-12 17:56</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2026-03-12 19:56</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
+      <c r="B119" t="n">
         <v>0.9767</v>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>L0118</t>
         </is>
@@ -2804,15 +2209,10 @@
           <t>2026-03-12 19:54</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2026-03-12 21:33</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
+      <c r="B120" t="n">
         <v>0.9757</v>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>L0119</t>
         </is>
@@ -2824,15 +2224,10 @@
           <t>2026-03-12 22:04</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2026-03-12 23:44</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
+      <c r="B121" t="n">
         <v>0.984</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>L0120</t>
         </is>
@@ -2844,15 +2239,10 @@
           <t>2026-03-13 00:03</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2026-03-13 01:11</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
+      <c r="B122" t="n">
         <v>0.9779</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>L0121</t>
         </is>
@@ -2864,15 +2254,10 @@
           <t>2026-03-13 02:03</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2026-03-13 03:49</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
+      <c r="B123" t="n">
         <v>0.9779</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>L0122</t>
         </is>
@@ -2884,15 +2269,10 @@
           <t>2026-03-13 04:02</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2026-03-13 05:52</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
+      <c r="B124" t="n">
         <v>0.9802999999999999</v>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>L0123</t>
         </is>
@@ -2904,15 +2284,10 @@
           <t>2026-03-13 05:53</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2026-03-13 07:42</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
+      <c r="B125" t="n">
         <v>0.9835</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>L0124</t>
         </is>
@@ -2924,15 +2299,10 @@
           <t>2026-03-13 07:53</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2026-03-13 09:47</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
+      <c r="B126" t="n">
         <v>0.9823</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>L0125</t>
         </is>
@@ -2944,15 +2314,10 @@
           <t>2026-03-13 09:51</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2026-03-13 10:52</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
+      <c r="B127" t="n">
         <v>0.9789</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>L0126</t>
         </is>
@@ -2964,15 +2329,10 @@
           <t>2026-03-13 11:51</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2026-03-13 13:09</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
+      <c r="B128" t="n">
         <v>0.9817</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>L0127</t>
         </is>
@@ -2984,15 +2344,10 @@
           <t>2026-03-13 14:08</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2026-03-13 14:53</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
+      <c r="B129" t="n">
         <v>0.9789</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>L0128</t>
         </is>
@@ -3004,15 +2359,10 @@
           <t>2026-03-13 16:07</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2026-03-13 17:44</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
+      <c r="B130" t="n">
         <v>0.98</v>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>L0129</t>
         </is>
@@ -3024,15 +2374,10 @@
           <t>2026-03-13 17:50</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2026-03-13 19:33</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
+      <c r="B131" t="n">
         <v>0.984</v>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>L0130</t>
         </is>
@@ -3044,15 +2389,10 @@
           <t>2026-03-13 20:08</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2026-03-13 20:55</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
+      <c r="B132" t="n">
         <v>0.977</v>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>L0131</t>
         </is>
@@ -3064,15 +2404,10 @@
           <t>2026-03-13 22:08</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2026-03-13 23:17</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
+      <c r="B133" t="n">
         <v>0.9856</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>L0132</t>
         </is>
@@ -3084,15 +2419,10 @@
           <t>2026-03-13 23:54</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2026-03-14 01:10</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
+      <c r="B134" t="n">
         <v>0.9862</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>L0133</t>
         </is>
@@ -3104,15 +2434,10 @@
           <t>2026-03-14 02:10</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2026-03-14 03:43</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
+      <c r="B135" t="n">
         <v>0.986</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>L0134</t>
         </is>
@@ -3124,15 +2449,10 @@
           <t>2026-03-14 04:06</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2026-03-14 05:22</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
+      <c r="B136" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>L0135</t>
         </is>
@@ -3144,15 +2464,10 @@
           <t>2026-03-14 05:51</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2026-03-14 07:34</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
+      <c r="B137" t="n">
         <v>0.9861</v>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>L0136</t>
         </is>
@@ -3164,15 +2479,10 @@
           <t>2026-03-14 08:07</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2026-03-14 09:59</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
+      <c r="B138" t="n">
         <v>0.9827</v>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>L0137</t>
         </is>
@@ -3184,15 +2494,10 @@
           <t>2026-03-14 10:10</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2026-03-14 11:52</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
+      <c r="B139" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>L0138</t>
         </is>
@@ -3204,15 +2509,10 @@
           <t>2026-03-14 12:01</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2026-03-14 13:40</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
+      <c r="B140" t="n">
         <v>0.9799</v>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>L0139</t>
         </is>
@@ -3224,15 +2524,10 @@
           <t>2026-03-14 14:09</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2026-03-14 15:50</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
+      <c r="B141" t="n">
         <v>0.9817</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>L0140</t>
         </is>
@@ -3244,15 +2539,10 @@
           <t>2026-03-14 16:07</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2026-03-14 17:21</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
+      <c r="B142" t="n">
         <v>0.9846</v>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>L0141</t>
         </is>
@@ -3264,15 +2554,10 @@
           <t>2026-03-14 17:50</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2026-03-14 19:15</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
+      <c r="B143" t="n">
         <v>0.9888</v>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>L0142</t>
         </is>
@@ -3284,15 +2569,10 @@
           <t>2026-03-14 19:54</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2026-03-14 21:31</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
+      <c r="B144" t="n">
         <v>0.9856</v>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>L0143</t>
         </is>
@@ -3304,15 +2584,10 @@
           <t>2026-03-14 22:04</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-03-14 23:05</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
+      <c r="B145" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>L0144</t>
         </is>
@@ -3324,15 +2599,10 @@
           <t>2026-03-15 00:01</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2026-03-15 01:36</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
+      <c r="B146" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>L0145</t>
         </is>
@@ -3344,15 +2614,10 @@
           <t>2026-03-15 01:52</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2026-03-15 03:18</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
+      <c r="B147" t="n">
         <v>0.9802999999999999</v>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>L0146</t>
         </is>
@@ -3364,15 +2629,10 @@
           <t>2026-03-15 04:01</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2026-03-15 05:40</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
+      <c r="B148" t="n">
         <v>0.9785</v>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>L0147</t>
         </is>
@@ -3384,15 +2644,10 @@
           <t>2026-03-15 05:52</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2026-03-15 07:21</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
+      <c r="B149" t="n">
         <v>0.9786</v>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>L0148</t>
         </is>
@@ -3404,15 +2659,10 @@
           <t>2026-03-15 08:00</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2026-03-15 09:15</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
+      <c r="B150" t="n">
         <v>0.9779</v>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>L0149</t>
         </is>
@@ -3424,15 +2674,10 @@
           <t>2026-03-15 10:09</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2026-03-15 11:15</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
+      <c r="B151" t="n">
         <v>0.982</v>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>L0150</t>
         </is>
@@ -3444,15 +2689,10 @@
           <t>2026-03-15 11:52</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2026-03-15 13:31</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
+      <c r="B152" t="n">
         <v>0.9807</v>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>L0151</t>
         </is>
@@ -3464,15 +2704,10 @@
           <t>2026-03-15 13:55</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-03-15 15:52</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
+      <c r="B153" t="n">
         <v>0.9815</v>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>L0152</t>
         </is>
@@ -3484,15 +2719,10 @@
           <t>2026-03-15 15:57</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2026-03-15 17:06</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
+      <c r="B154" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>L0153</t>
         </is>
@@ -3504,15 +2734,10 @@
           <t>2026-03-15 17:56</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2026-03-15 19:08</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
+      <c r="B155" t="n">
         <v>0.982</v>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>L0154</t>
         </is>
@@ -3524,15 +2749,10 @@
           <t>2026-03-15 19:50</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2026-03-15 20:52</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
+      <c r="B156" t="n">
         <v>0.9852</v>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>L0155</t>
         </is>
@@ -3544,15 +2764,10 @@
           <t>2026-03-15 22:02</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:52</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
+      <c r="B157" t="n">
         <v>0.9864000000000001</v>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>L0156</t>
         </is>
@@ -3564,15 +2779,10 @@
           <t>2026-03-16 00:04</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2026-03-16 00:54</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
+      <c r="B158" t="n">
         <v>0.9864000000000001</v>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>L0157</t>
         </is>
@@ -3584,15 +2794,10 @@
           <t>2026-03-16 02:02</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2026-03-16 03:51</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
+      <c r="B159" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>L0158</t>
         </is>
@@ -3604,15 +2809,10 @@
           <t>2026-03-16 04:02</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2026-03-16 05:43</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
+      <c r="B160" t="n">
         <v>0.9868</v>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>L0159</t>
         </is>
@@ -3624,15 +2824,10 @@
           <t>2026-03-16 05:52</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2026-03-16 06:47</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
+      <c r="B161" t="n">
         <v>0.9928</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>L0160</t>
         </is>
@@ -3644,15 +2839,10 @@
           <t>2026-03-16 08:00</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2026-03-16 08:53</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
+      <c r="B162" t="n">
         <v>0.9871</v>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>L0161</t>
         </is>
@@ -3664,15 +2854,10 @@
           <t>2026-03-16 10:04</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2026-03-16 11:22</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
+      <c r="B163" t="n">
         <v>0.9808</v>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>L0162</t>
         </is>
@@ -3684,15 +2869,10 @@
           <t>2026-03-16 12:04</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2026-03-16 13:57</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
+      <c r="B164" t="n">
         <v>0.9823</v>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>L0163</t>
         </is>
@@ -3704,15 +2884,10 @@
           <t>2026-03-16 14:04</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2026-03-16 15:11</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
+      <c r="B165" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>L0164</t>
         </is>
@@ -3724,15 +2899,10 @@
           <t>2026-03-16 16:01</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2026-03-16 17:16</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
+      <c r="B166" t="n">
         <v>0.9815</v>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>L0165</t>
         </is>
@@ -3744,15 +2914,10 @@
           <t>2026-03-16 17:58</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:49</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
+      <c r="B167" t="n">
         <v>0.9796</v>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>L0166</t>
         </is>
@@ -3764,15 +2929,10 @@
           <t>2026-03-16 19:50</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2026-03-16 21:00</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
+      <c r="B168" t="n">
         <v>0.9844000000000001</v>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>L0167</t>
         </is>
@@ -3784,15 +2944,10 @@
           <t>2026-03-16 22:07</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2026-03-16 22:58</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
+      <c r="B169" t="n">
         <v>0.9852</v>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>L0168</t>
         </is>
@@ -3804,15 +2959,10 @@
           <t>2026-03-16 23:53</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2026-03-17 01:28</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
+      <c r="B170" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>L0169</t>
         </is>
@@ -3824,15 +2974,10 @@
           <t>2026-03-17 01:59</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2026-03-17 03:58</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
+      <c r="B171" t="n">
         <v>0.9814000000000001</v>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>L0170</t>
         </is>
@@ -3844,15 +2989,10 @@
           <t>2026-03-17 03:53</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2026-03-17 05:31</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
+      <c r="B172" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>L0171</t>
         </is>
@@ -3864,15 +3004,10 @@
           <t>2026-03-17 06:05</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2026-03-17 06:57</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
+      <c r="B173" t="n">
         <v>0.9812</v>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>L0172</t>
         </is>
@@ -3884,15 +3019,10 @@
           <t>2026-03-17 07:58</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2026-03-17 09:42</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
+      <c r="B174" t="n">
         <v>0.9829</v>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>L0173</t>
         </is>
@@ -3904,15 +3034,10 @@
           <t>2026-03-17 09:51</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2026-03-17 11:40</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
+      <c r="B175" t="n">
         <v>0.98</v>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>L0174</t>
         </is>
@@ -3924,15 +3049,10 @@
           <t>2026-03-17 12:09</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2026-03-17 13:52</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
+      <c r="B176" t="n">
         <v>0.9863</v>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>L0175</t>
         </is>
@@ -3944,15 +3064,10 @@
           <t>2026-03-17 13:50</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2026-03-17 14:45</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
+      <c r="B177" t="n">
         <v>0.9797</v>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>L0176</t>
         </is>
@@ -3964,15 +3079,10 @@
           <t>2026-03-17 16:02</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2026-03-17 17:28</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
+      <c r="B178" t="n">
         <v>0.9796</v>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>L0177</t>
         </is>
@@ -3984,15 +3094,10 @@
           <t>2026-03-17 17:53</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2026-03-17 18:42</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
+      <c r="B179" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>L0178</t>
         </is>
@@ -4004,15 +3109,10 @@
           <t>2026-03-17 19:52</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:06</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
+      <c r="B180" t="n">
         <v>0.9808</v>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>L0179</t>
         </is>
@@ -4024,15 +3124,10 @@
           <t>2026-03-17 22:08</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2026-03-17 23:10</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
+      <c r="B181" t="n">
         <v>0.9815</v>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>L0180</t>
         </is>
@@ -4044,15 +3139,10 @@
           <t>2026-03-17 23:52</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2026-03-18 00:54</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
+      <c r="B182" t="n">
         <v>0.9858</v>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>L0181</t>
         </is>
@@ -4064,15 +3154,10 @@
           <t>2026-03-18 01:54</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2026-03-18 02:53</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
+      <c r="B183" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>L0182</t>
         </is>
@@ -4084,15 +3169,10 @@
           <t>2026-03-18 03:58</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2026-03-18 05:14</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
+      <c r="B184" t="n">
         <v>0.9804</v>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>L0183</t>
         </is>
@@ -4104,15 +3184,10 @@
           <t>2026-03-18 05:54</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2026-03-18 07:45</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
+      <c r="B185" t="n">
         <v>0.9788</v>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>L0184</t>
         </is>
@@ -4124,15 +3199,10 @@
           <t>2026-03-18 07:53</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2026-03-18 08:40</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
+      <c r="B186" t="n">
         <v>0.9876</v>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>L0185</t>
         </is>
@@ -4144,15 +3214,10 @@
           <t>2026-03-18 10:06</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2026-03-18 11:47</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
+      <c r="B187" t="n">
         <v>0.9883</v>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>L0186</t>
         </is>
@@ -4164,15 +3229,10 @@
           <t>2026-03-18 12:05</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2026-03-18 13:40</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
+      <c r="B188" t="n">
         <v>0.9838</v>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>L0187</t>
         </is>
@@ -4184,15 +3244,10 @@
           <t>2026-03-18 14:00</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2026-03-18 15:02</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
+      <c r="B189" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>L0188</t>
         </is>
@@ -4204,15 +3259,10 @@
           <t>2026-03-18 15:54</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>2026-03-18 17:15</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
+      <c r="B190" t="n">
         <v>0.9776</v>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>L0189</t>
         </is>
@@ -4224,15 +3274,10 @@
           <t>2026-03-18 17:52</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>2026-03-18 19:32</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
+      <c r="B191" t="n">
         <v>0.9795</v>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>L0190</t>
         </is>
@@ -4244,15 +3289,10 @@
           <t>2026-03-18 19:55</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2026-03-18 21:23</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
+      <c r="B192" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>L0191</t>
         </is>
@@ -4264,15 +3304,10 @@
           <t>2026-03-18 22:01</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2026-03-18 23:51</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
+      <c r="B193" t="n">
         <v>0.9893</v>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>L0192</t>
         </is>
@@ -4284,15 +3319,10 @@
           <t>2026-03-18 23:57</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2026-03-19 00:48</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
+      <c r="B194" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>L0193</t>
         </is>
@@ -4304,15 +3334,10 @@
           <t>2026-03-19 02:02</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2026-03-19 03:59</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
+      <c r="B195" t="n">
         <v>0.9829</v>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>L0194</t>
         </is>
@@ -4324,15 +3349,10 @@
           <t>2026-03-19 04:10</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2026-03-19 05:44</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
+      <c r="B196" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>L0195</t>
         </is>
@@ -4344,15 +3364,10 @@
           <t>2026-03-19 05:53</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2026-03-19 07:40</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
+      <c r="B197" t="n">
         <v>0.9843</v>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>L0196</t>
         </is>
@@ -4364,15 +3379,10 @@
           <t>2026-03-19 07:58</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2026-03-19 09:39</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
+      <c r="B198" t="n">
         <v>0.9856</v>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>L0197</t>
         </is>
@@ -4384,15 +3394,10 @@
           <t>2026-03-19 10:07</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2026-03-19 10:57</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
+      <c r="B199" t="n">
         <v>0.9881</v>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>L0198</t>
         </is>
@@ -4404,15 +3409,10 @@
           <t>2026-03-19 12:06</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>2026-03-19 13:05</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
+      <c r="B200" t="n">
         <v>0.9855</v>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>L0199</t>
         </is>
@@ -4424,15 +3424,10 @@
           <t>2026-03-19 13:54</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>2026-03-19 14:39</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
+      <c r="B201" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>L0200</t>
         </is>
@@ -4444,15 +3439,10 @@
           <t>2026-03-19 16:03</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>2026-03-19 17:40</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
+      <c r="B202" t="n">
         <v>0.9808</v>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>L0201</t>
         </is>
@@ -4464,15 +3454,10 @@
           <t>2026-03-19 18:04</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>2026-03-19 19:20</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
+      <c r="B203" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>L0202</t>
         </is>
@@ -4484,15 +3469,10 @@
           <t>2026-03-19 19:58</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>2026-03-19 21:21</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
+      <c r="B204" t="n">
         <v>0.9775</v>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>L0203</t>
         </is>
@@ -4504,15 +3484,10 @@
           <t>2026-03-19 21:50</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>2026-03-19 23:02</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
+      <c r="B205" t="n">
         <v>0.9798</v>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>L0204</t>
         </is>
@@ -4524,15 +3499,10 @@
           <t>2026-03-19 23:55</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>2026-03-20 01:20</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
+      <c r="B206" t="n">
         <v>0.978</v>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>L0205</t>
         </is>
@@ -4544,15 +3514,10 @@
           <t>2026-03-20 01:55</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>2026-03-20 02:45</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
+      <c r="B207" t="n">
         <v>0.979</v>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>L0206</t>
         </is>
@@ -4564,15 +3529,10 @@
           <t>2026-03-20 04:07</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>2026-03-20 06:07</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
+      <c r="B208" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>L0207</t>
         </is>
@@ -4584,15 +3544,10 @@
           <t>2026-03-20 06:00</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>2026-03-20 07:38</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
+      <c r="B209" t="n">
         <v>0.9837</v>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>L0208</t>
         </is>
@@ -4604,15 +3559,10 @@
           <t>2026-03-20 08:06</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>2026-03-20 09:37</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
+      <c r="B210" t="n">
         <v>0.9787</v>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>L0209</t>
         </is>
@@ -4624,15 +3574,10 @@
           <t>2026-03-20 10:02</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2026-03-20 11:53</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
+      <c r="B211" t="n">
         <v>0.9797</v>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>L0210</t>
         </is>
@@ -4644,15 +3589,10 @@
           <t>2026-03-20 11:53</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:13</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
+      <c r="B212" t="n">
         <v>0.9792</v>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>L0211</t>
         </is>
@@ -4664,15 +3604,10 @@
           <t>2026-03-20 13:57</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2026-03-20 15:51</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
+      <c r="B213" t="n">
         <v>0.9774</v>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>L0212</t>
         </is>
@@ -4684,15 +3619,10 @@
           <t>2026-03-20 15:57</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2026-03-20 16:59</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
+      <c r="B214" t="n">
         <v>0.9802</v>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>L0213</t>
         </is>
@@ -4704,15 +3634,10 @@
           <t>2026-03-20 17:55</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2026-03-20 19:54</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
+      <c r="B215" t="n">
         <v>0.9807</v>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>L0214</t>
         </is>
@@ -4724,15 +3649,10 @@
           <t>2026-03-20 20:09</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2026-03-20 21:53</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
+      <c r="B216" t="n">
         <v>0.9814000000000001</v>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>L0215</t>
         </is>
@@ -4744,15 +3664,10 @@
           <t>2026-03-20 22:06</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2026-03-20 23:58</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
+      <c r="B217" t="n">
         <v>0.9835</v>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>L0216</t>
         </is>
@@ -4764,15 +3679,10 @@
           <t>2026-03-21 00:00</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>2026-03-21 00:53</t>
-        </is>
-      </c>
-      <c r="C218" t="n">
+      <c r="B218" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>L0217</t>
         </is>
@@ -4784,15 +3694,10 @@
           <t>2026-03-21 01:54</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>2026-03-21 02:55</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
+      <c r="B219" t="n">
         <v>0.987</v>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>L0218</t>
         </is>
@@ -4804,15 +3709,10 @@
           <t>2026-03-21 04:07</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2026-03-21 05:21</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
+      <c r="B220" t="n">
         <v>0.9902</v>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>L0219</t>
         </is>
@@ -4824,15 +3724,10 @@
           <t>2026-03-21 05:56</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2026-03-21 07:38</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
+      <c r="B221" t="n">
         <v>0.9888</v>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>L0220</t>
         </is>
@@ -4844,15 +3739,10 @@
           <t>2026-03-21 08:01</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2026-03-21 09:38</t>
-        </is>
-      </c>
-      <c r="C222" t="n">
+      <c r="B222" t="n">
         <v>0.9862</v>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>L0221</t>
         </is>
@@ -4864,15 +3754,10 @@
           <t>2026-03-21 09:52</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>2026-03-21 11:21</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
+      <c r="B223" t="n">
         <v>0.9831</v>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>L0222</t>
         </is>
@@ -4884,15 +3769,10 @@
           <t>2026-03-21 11:59</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>2026-03-21 13:59</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
+      <c r="B224" t="n">
         <v>0.9787</v>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>L0223</t>
         </is>
@@ -4904,15 +3784,10 @@
           <t>2026-03-21 13:52</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2026-03-21 15:22</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
+      <c r="B225" t="n">
         <v>0.982</v>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>L0224</t>
         </is>
@@ -4924,15 +3799,10 @@
           <t>2026-03-21 16:02</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>2026-03-21 18:02</t>
-        </is>
-      </c>
-      <c r="C226" t="n">
+      <c r="B226" t="n">
         <v>0.9765</v>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>L0225</t>
         </is>
@@ -4944,15 +3814,10 @@
           <t>2026-03-21 18:05</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2026-03-21 18:50</t>
-        </is>
-      </c>
-      <c r="C227" t="n">
+      <c r="B227" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>L0226</t>
         </is>
@@ -4964,15 +3829,10 @@
           <t>2026-03-21 20:03</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2026-03-21 21:37</t>
-        </is>
-      </c>
-      <c r="C228" t="n">
+      <c r="B228" t="n">
         <v>0.987</v>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>L0227</t>
         </is>
@@ -4984,15 +3844,10 @@
           <t>2026-03-22 14:05</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2026-03-22 15:47</t>
-        </is>
-      </c>
-      <c r="C229" t="n">
+      <c r="B229" t="n">
         <v>0.9794</v>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>L0228</t>
         </is>
@@ -5004,15 +3859,10 @@
           <t>2026-03-22 16:00</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>2026-03-22 17:36</t>
-        </is>
-      </c>
-      <c r="C230" t="n">
+      <c r="B230" t="n">
         <v>0.978</v>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>L0229</t>
         </is>
@@ -5024,15 +3874,10 @@
           <t>2026-03-22 18:09</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2026-03-22 19:46</t>
-        </is>
-      </c>
-      <c r="C231" t="n">
+      <c r="B231" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t>L0230</t>
         </is>
@@ -5044,15 +3889,10 @@
           <t>2026-03-22 20:05</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2026-03-22 21:50</t>
-        </is>
-      </c>
-      <c r="C232" t="n">
+      <c r="B232" t="n">
         <v>0.981</v>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>L0231</t>
         </is>
@@ -5064,15 +3904,10 @@
           <t>2026-03-22 21:55</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2026-03-22 22:56</t>
-        </is>
-      </c>
-      <c r="C233" t="n">
+      <c r="B233" t="n">
         <v>0.9796</v>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>L0232</t>
         </is>
@@ -5084,15 +3919,10 @@
           <t>2026-03-22 23:58</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2026-03-23 00:48</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
+      <c r="B234" t="n">
         <v>0.9819</v>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>L0233</t>
         </is>
@@ -5104,15 +3934,10 @@
           <t>2026-03-23 01:51</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2026-03-23 02:59</t>
-        </is>
-      </c>
-      <c r="C235" t="n">
+      <c r="B235" t="n">
         <v>0.9901</v>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>L0234</t>
         </is>
@@ -5124,15 +3949,10 @@
           <t>2026-03-23 04:02</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2026-03-23 05:30</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
+      <c r="B236" t="n">
         <v>0.9816</v>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="C236" t="inlineStr">
         <is>
           <t>L0235</t>
         </is>
@@ -5144,15 +3964,10 @@
           <t>2026-03-23 06:06</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2026-03-23 07:26</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
+      <c r="B237" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>L0236</t>
         </is>
@@ -5164,15 +3979,10 @@
           <t>2026-03-23 08:00</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>2026-03-23 09:42</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
+      <c r="B238" t="n">
         <v>0.9772</v>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>L0237</t>
         </is>
@@ -5184,15 +3994,10 @@
           <t>2026-03-23 10:09</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>2026-03-23 11:48</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
+      <c r="B239" t="n">
         <v>0.98</v>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>L0238</t>
         </is>
@@ -5204,15 +4009,10 @@
           <t>2026-03-23 11:51</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2026-03-23 13:09</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
+      <c r="B240" t="n">
         <v>0.9798</v>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>L0239</t>
         </is>
@@ -5224,15 +4024,10 @@
           <t>2026-03-23 13:53</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2026-03-23 14:54</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
+      <c r="B241" t="n">
         <v>0.9831</v>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>L0240</t>
         </is>
@@ -5244,15 +4039,10 @@
           <t>2026-03-23 15:50</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2026-03-23 16:56</t>
-        </is>
-      </c>
-      <c r="C242" t="n">
+      <c r="B242" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>L0241</t>
         </is>
@@ -5264,15 +4054,10 @@
           <t>2026-03-23 17:59</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2026-03-23 18:59</t>
-        </is>
-      </c>
-      <c r="C243" t="n">
+      <c r="B243" t="n">
         <v>0.9829</v>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>L0242</t>
         </is>
@@ -5284,15 +4069,10 @@
           <t>2026-03-23 19:51</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2026-03-23 21:08</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
+      <c r="B244" t="n">
         <v>0.9813</v>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>L0243</t>
         </is>
@@ -5304,15 +4084,10 @@
           <t>2026-03-23 22:07</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2026-03-23 23:59</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
+      <c r="B245" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>L0244</t>
         </is>
@@ -5324,15 +4099,10 @@
           <t>2026-03-24 00:00</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2026-03-24 01:53</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
+      <c r="B246" t="n">
         <v>0.9809</v>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>L0245</t>
         </is>
@@ -5344,15 +4114,10 @@
           <t>2026-03-24 02:00</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2026-03-24 03:54</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
+      <c r="B247" t="n">
         <v>0.9816</v>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>L0246</t>
         </is>
@@ -5364,15 +4129,10 @@
           <t>2026-03-24 03:55</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>2026-03-24 05:16</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
+      <c r="B248" t="n">
         <v>0.9771</v>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>L0247</t>
         </is>
@@ -5384,15 +4144,10 @@
           <t>2026-03-24 05:55</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2026-03-24 07:37</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
+      <c r="B249" t="n">
         <v>0.9856</v>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>L0248</t>
         </is>
@@ -5404,15 +4159,10 @@
           <t>2026-03-24 07:59</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2026-03-24 09:35</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
+      <c r="B250" t="n">
         <v>0.9814000000000001</v>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>L0249</t>
         </is>
@@ -5424,15 +4174,10 @@
           <t>2026-03-24 09:59</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2026-03-24 11:05</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
+      <c r="B251" t="n">
         <v>0.9806</v>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>L0250</t>
         </is>
@@ -5444,15 +4189,10 @@
           <t>2026-03-24 12:03</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2026-03-24 13:18</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
+      <c r="B252" t="n">
         <v>0.982</v>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>L0251</t>
         </is>
@@ -5464,15 +4204,10 @@
           <t>2026-03-24 13:58</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2026-03-24 14:44</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
+      <c r="B253" t="n">
         <v>0.9816</v>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>L0252</t>
         </is>
@@ -5484,15 +4219,10 @@
           <t>2026-03-24 15:50</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2026-03-24 16:47</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
+      <c r="B254" t="n">
         <v>0.9</v>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>L0253</t>
         </is>
@@ -5504,15 +4234,10 @@
           <t>2026-03-24 18:10</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2026-03-24 19:26</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
+      <c r="B255" t="n">
         <v>0.9817</v>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>L0254</t>
         </is>
@@ -5524,15 +4249,10 @@
           <t>2026-03-24 20:01</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2026-03-24 21:47</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
+      <c r="B256" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>L0255</t>
         </is>
@@ -5544,15 +4264,10 @@
           <t>2026-03-24 22:09</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>2026-03-24 23:11</t>
-        </is>
-      </c>
-      <c r="C257" t="n">
+      <c r="B257" t="n">
         <v>0.9831</v>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>L0256</t>
         </is>
@@ -5564,15 +4279,10 @@
           <t>2026-03-25 00:06</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2026-03-25 01:15</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
+      <c r="B258" t="n">
         <v>0.9836</v>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>L0257</t>
         </is>
@@ -5584,15 +4294,10 @@
           <t>2026-03-25 01:54</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2026-03-25 03:05</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
+      <c r="B259" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>L0258</t>
         </is>
@@ -5604,15 +4309,10 @@
           <t>2026-03-25 03:51</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>2026-03-25 04:57</t>
-        </is>
-      </c>
-      <c r="C260" t="n">
+      <c r="B260" t="n">
         <v>0.9858</v>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>L0259</t>
         </is>
@@ -5624,15 +4324,10 @@
           <t>2026-03-25 05:56</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2026-03-25 07:14</t>
-        </is>
-      </c>
-      <c r="C261" t="n">
+      <c r="B261" t="n">
         <v>0.9818</v>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>L0260</t>
         </is>
@@ -5644,15 +4339,10 @@
           <t>2026-03-25 07:54</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2026-03-25 09:29</t>
-        </is>
-      </c>
-      <c r="C262" t="n">
+      <c r="B262" t="n">
         <v>0.9853</v>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>L0261</t>
         </is>
@@ -5664,15 +4354,10 @@
           <t>2026-03-25 10:03</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2026-03-25 11:51</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
+      <c r="B263" t="n">
         <v>0.9799</v>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>L0262</t>
         </is>
@@ -5684,15 +4369,10 @@
           <t>2026-03-25 12:10</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>2026-03-25 14:01</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
+      <c r="B264" t="n">
         <v>0.984</v>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>L0263</t>
         </is>
@@ -5704,15 +4384,10 @@
           <t>2026-03-25 14:05</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2026-03-25 15:27</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
+      <c r="B265" t="n">
         <v>0.9815</v>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>L0264</t>
         </is>
@@ -5724,15 +4399,10 @@
           <t>2026-03-25 15:53</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-03-25 17:37</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
+      <c r="B266" t="n">
         <v>0.9887</v>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>L0265</t>
         </is>
@@ -5744,15 +4414,10 @@
           <t>2026-03-25 17:53</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-03-25 19:18</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
+      <c r="B267" t="n">
         <v>0.9817</v>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>L0266</t>
         </is>
@@ -5764,15 +4429,10 @@
           <t>2026-03-25 19:53</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-03-25 21:30</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
+      <c r="B268" t="n">
         <v>0.9801</v>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>L0267</t>
         </is>
@@ -5784,15 +4444,10 @@
           <t>2026-03-25 22:01</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-03-25 23:41</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
+      <c r="B269" t="n">
         <v>0.9815</v>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>L0268</t>
         </is>
@@ -5804,15 +4459,10 @@
           <t>2026-03-25 23:52</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2026-03-26 01:05</t>
-        </is>
-      </c>
-      <c r="C270" t="n">
+      <c r="B270" t="n">
         <v>0.9798</v>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>L0269</t>
         </is>
@@ -5824,15 +4474,10 @@
           <t>2026-03-26 01:59</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2026-03-26 02:58</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
+      <c r="B271" t="n">
         <v>0.9833</v>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>L0270</t>
         </is>
@@ -5844,15 +4489,10 @@
           <t>2026-03-26 03:54</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-03-26 04:56</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
+      <c r="B272" t="n">
         <v>0.9788</v>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="C272" t="inlineStr">
         <is>
           <t>L0271</t>
         </is>
@@ -5864,15 +4504,10 @@
           <t>2026-03-26 06:09</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-03-26 07:21</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
+      <c r="B273" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>L0272</t>
         </is>
@@ -5884,15 +4519,10 @@
           <t>2026-03-26 07:55</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2026-03-26 09:19</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
+      <c r="B274" t="n">
         <v>0.9855</v>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>L0273</t>
         </is>
@@ -5904,15 +4534,10 @@
           <t>2026-03-26 10:03</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2026-03-26 11:29</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
+      <c r="B275" t="n">
         <v>0.9802</v>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="C275" t="inlineStr">
         <is>
           <t>L0274</t>
         </is>
@@ -5924,15 +4549,10 @@
           <t>2026-03-26 12:08</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2026-03-26 13:51</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
+      <c r="B276" t="n">
         <v>0.9817</v>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>L0275</t>
         </is>
@@ -5944,15 +4564,10 @@
           <t>2026-03-26 14:07</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2026-03-26 15:03</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
+      <c r="B277" t="n">
         <v>0.9796</v>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>L0276</t>
         </is>
@@ -5964,15 +4579,10 @@
           <t>2026-03-26 16:09</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2026-03-26 17:00</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
+      <c r="B278" t="n">
         <v>0.9802</v>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>L0277</t>
         </is>
@@ -5984,15 +4594,10 @@
           <t>2026-03-26 17:59</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2026-03-26 19:26</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
+      <c r="B279" t="n">
         <v>0.983</v>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>L0278</t>
         </is>
@@ -6004,15 +4609,10 @@
           <t>2026-03-26 19:56</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-03-26 21:42</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
+      <c r="B280" t="n">
         <v>0.9802999999999999</v>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>L0279</t>
         </is>
@@ -6024,15 +4624,10 @@
           <t>2026-03-26 22:09</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-03-26 23:55</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
+      <c r="B281" t="n">
         <v>0.9856</v>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>L0280</t>
         </is>
@@ -6044,15 +4639,10 @@
           <t>2026-03-26 23:55</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-03-27 01:33</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
+      <c r="B282" t="n">
         <v>0.9801</v>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>L0281</t>
         </is>
@@ -6064,15 +4654,10 @@
           <t>2026-03-27 01:56</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-03-27 03:00</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
+      <c r="B283" t="n">
         <v>0.9822</v>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>L0282</t>
         </is>
@@ -6084,15 +4669,10 @@
           <t>2026-03-27 03:58</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-03-27 05:32</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
+      <c r="B284" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>L0283</t>
         </is>
@@ -6104,15 +4684,10 @@
           <t>2026-03-27 05:56</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-03-27 07:05</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
+      <c r="B285" t="n">
         <v>0.9786</v>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="C285" t="inlineStr">
         <is>
           <t>L0284</t>
         </is>
@@ -6124,15 +4699,10 @@
           <t>2026-03-27 07:58</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-03-27 09:43</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
+      <c r="B286" t="n">
         <v>0.9808</v>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>L0285</t>
         </is>
@@ -6144,15 +4714,10 @@
           <t>2026-03-27 10:00</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-03-27 11:57</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
+      <c r="B287" t="n">
         <v>0.9848</v>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>L0286</t>
         </is>
@@ -6164,15 +4729,10 @@
           <t>2026-03-27 11:57</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-03-27 13:20</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
+      <c r="B288" t="n">
         <v>0.9873</v>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>L0287</t>
         </is>
@@ -6184,15 +4744,10 @@
           <t>2026-03-27 13:56</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-03-27 15:19</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
+      <c r="B289" t="n">
         <v>0.9865</v>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="C289" t="inlineStr">
         <is>
           <t>L0288</t>
         </is>
@@ -6204,15 +4759,10 @@
           <t>2026-03-27 15:57</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-03-27 17:21</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
+      <c r="B290" t="n">
         <v>0.9797</v>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>L0289</t>
         </is>
@@ -6224,15 +4774,10 @@
           <t>2026-03-27 18:07</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-03-27 19:09</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
+      <c r="B291" t="n">
         <v>0.9835</v>
       </c>
-      <c r="D291" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>L0290</t>
         </is>
@@ -6244,15 +4789,10 @@
           <t>2026-03-27 20:03</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-03-27 21:36</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
+      <c r="B292" t="n">
         <v>0.9825</v>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="C292" t="inlineStr">
         <is>
           <t>L0291</t>
         </is>
@@ -6264,15 +4804,10 @@
           <t>2026-03-27 21:53</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:04</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
+      <c r="B293" t="n">
         <v>0.9876</v>
       </c>
-      <c r="D293" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>L0292</t>
         </is>
@@ -6284,15 +4819,10 @@
           <t>2026-03-28 00:01</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-03-28 01:50</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
+      <c r="B294" t="n">
         <v>0.9883999999999999</v>
       </c>
-      <c r="D294" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>L0293</t>
         </is>
@@ -6304,15 +4834,10 @@
           <t>2026-03-28 01:58</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-03-28 03:04</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
+      <c r="B295" t="n">
         <v>0.983</v>
       </c>
-      <c r="D295" t="inlineStr">
+      <c r="C295" t="inlineStr">
         <is>
           <t>L0294</t>
         </is>
@@ -6324,15 +4849,10 @@
           <t>2026-03-28 03:58</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-03-28 05:15</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
+      <c r="B296" t="n">
         <v>0.9808</v>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="C296" t="inlineStr">
         <is>
           <t>L0295</t>
         </is>
@@ -6344,15 +4864,10 @@
           <t>2026-03-28 06:08</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-03-28 07:19</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
+      <c r="B297" t="n">
         <v>0.9831</v>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="C297" t="inlineStr">
         <is>
           <t>L0296</t>
         </is>
@@ -6364,15 +4879,10 @@
           <t>2026-03-28 08:05</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-03-28 09:39</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
+      <c r="B298" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>L0297</t>
         </is>
@@ -6384,15 +4894,10 @@
           <t>2026-03-28 09:57</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-03-28 11:54</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
+      <c r="B299" t="n">
         <v>0.9858</v>
       </c>
-      <c r="D299" t="inlineStr">
+      <c r="C299" t="inlineStr">
         <is>
           <t>L0298</t>
         </is>
@@ -6404,15 +4909,10 @@
           <t>2026-03-28 11:54</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-03-28 12:42</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
+      <c r="B300" t="n">
         <v>0.985</v>
       </c>
-      <c r="D300" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>L0299</t>
         </is>
@@ -6424,15 +4924,10 @@
           <t>2026-03-28 13:58</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:34</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
+      <c r="B301" t="n">
         <v>0.9828</v>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>L0300</t>
         </is>
@@ -6444,15 +4939,10 @@
           <t>2026-03-28 16:00</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:51</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
+      <c r="B302" t="n">
         <v>0.9855</v>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>L0301</t>
         </is>
@@ -6464,15 +4954,10 @@
           <t>2026-03-28 18:07</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-03-28 19:57</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
+      <c r="B303" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="C303" t="inlineStr">
         <is>
           <t>L0302</t>
         </is>
@@ -6484,15 +4969,10 @@
           <t>2026-03-28 19:57</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-03-28 21:22</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
+      <c r="B304" t="n">
         <v>0.9799</v>
       </c>
-      <c r="D304" t="inlineStr">
+      <c r="C304" t="inlineStr">
         <is>
           <t>L0303</t>
         </is>
@@ -6504,15 +4984,10 @@
           <t>2026-03-28 22:07</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-03-28 23:41</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
+      <c r="B305" t="n">
         <v>0.9792999999999999</v>
       </c>
-      <c r="D305" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>L0304</t>
         </is>
@@ -6524,15 +4999,10 @@
           <t>2026-03-28 23:58</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-03-29 01:10</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
+      <c r="B306" t="n">
         <v>0.9813</v>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>L0305</t>
         </is>
@@ -6544,15 +5014,10 @@
           <t>2026-03-29 02:06</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-03-29 03:41</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
+      <c r="B307" t="n">
         <v>0.9804</v>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="C307" t="inlineStr">
         <is>
           <t>L0306</t>
         </is>
@@ -6564,15 +5029,10 @@
           <t>2026-03-29 03:55</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-03-29 05:47</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
+      <c r="B308" t="n">
         <v>0.9813</v>
       </c>
-      <c r="D308" t="inlineStr">
+      <c r="C308" t="inlineStr">
         <is>
           <t>L0307</t>
         </is>
@@ -6584,15 +5044,10 @@
           <t>2026-03-29 05:54</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-03-29 07:10</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
+      <c r="B309" t="n">
         <v>0.9816</v>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="C309" t="inlineStr">
         <is>
           <t>L0308</t>
         </is>
@@ -6604,15 +5059,10 @@
           <t>2026-03-29 08:08</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-03-29 09:39</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
+      <c r="B310" t="n">
         <v>0.9804</v>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="C310" t="inlineStr">
         <is>
           <t>L0309</t>
         </is>
@@ -6624,15 +5074,10 @@
           <t>2026-03-29 09:54</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-03-29 11:38</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
+      <c r="B311" t="n">
         <v>0.9833</v>
       </c>
-      <c r="D311" t="inlineStr">
+      <c r="C311" t="inlineStr">
         <is>
           <t>L0310</t>
         </is>
@@ -6644,15 +5089,10 @@
           <t>2026-03-29 11:52</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-03-29 12:50</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
+      <c r="B312" t="n">
         <v>0.9841</v>
       </c>
-      <c r="D312" t="inlineStr">
+      <c r="C312" t="inlineStr">
         <is>
           <t>L0311</t>
         </is>
@@ -6664,15 +5104,10 @@
           <t>2026-03-29 13:54</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-03-29 15:03</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
+      <c r="B313" t="n">
         <v>0.9818</v>
       </c>
-      <c r="D313" t="inlineStr">
+      <c r="C313" t="inlineStr">
         <is>
           <t>L0312</t>
         </is>
@@ -6684,15 +5119,10 @@
           <t>2026-03-29 16:07</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-03-29 17:46</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
+      <c r="B314" t="n">
         <v>0.9797</v>
       </c>
-      <c r="D314" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>L0313</t>
         </is>
@@ -6704,15 +5134,10 @@
           <t>2026-03-29 17:54</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-03-29 18:58</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
+      <c r="B315" t="n">
         <v>0.9837</v>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="C315" t="inlineStr">
         <is>
           <t>L0314</t>
         </is>
@@ -6724,15 +5149,10 @@
           <t>2026-03-29 19:51</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-03-29 21:50</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
+      <c r="B316" t="n">
         <v>0.9805</v>
       </c>
-      <c r="D316" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>L0315</t>
         </is>
@@ -6744,15 +5164,10 @@
           <t>2026-03-29 22:10</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-03-29 23:05</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
+      <c r="B317" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>L0316</t>
         </is>
